--- a/results/Int Task Remove ACC -0.1/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.1/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>-0.00170777765801278</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02805914284943647</v>
+        <v>0.0280591873514529</v>
       </c>
       <c r="F3" t="n">
         <v>0.003156378283689571</v>
@@ -1166,28 +1166,28 @@
         <v>0.0395377836992271</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002510025101939821</v>
+        <v>0.002506607466943239</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001447940373905043</v>
+        <v>0.0001414383326925184</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03207517948585188</v>
+        <v>0.03206843759894116</v>
       </c>
       <c r="K3" t="n">
+        <v>0.01813175043810188</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.01813524083949804</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.01813845937828143</v>
       </c>
       <c r="M3" t="n">
         <v>0.01831280909740992</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0136634579136841</v>
+        <v>0.01366351009131764</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04821604010637132</v>
+        <v>0.04821599992670676</v>
       </c>
       <c r="P3" t="n">
         <v>0.01298480022795228</v>
@@ -1196,7 +1196,7 @@
         <v>0.01245589943238867</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01580216413180761</v>
+        <v>0.01580904479662041</v>
       </c>
       <c r="S3" t="n">
         <v>0.2865593935213304</v>
@@ -1208,7 +1208,7 @@
         <v>0.1310837128561827</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001448842320722554</v>
+        <v>0.0001483018670688375</v>
       </c>
       <c r="W3" t="n">
         <v>0.006876042604380478</v>
@@ -1232,13 +1232,13 @@
         <v>0.03905640604867168</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1339073818342977</v>
+        <v>0.1339041632955143</v>
       </c>
       <c r="AE3" t="n">
         <v>0.2418132554717633</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09735780466496594</v>
+        <v>0.09736102320374931</v>
       </c>
       <c r="AG3" t="n">
         <v>0.1381391609225832</v>
@@ -1298,19 +1298,19 @@
         <v>-0.007640724176767331</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.00891744556799411</v>
+        <v>0.008910464765201789</v>
       </c>
       <c r="BA3" t="n">
         <v>0.01076888930261176</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0001543160207305775</v>
+        <v>0.0001510319484809876</v>
       </c>
       <c r="BC3" t="n">
+        <v>-0.0002654608064157582</v>
+      </c>
+      <c r="BD3" t="n">
         <v>-0.0002619704050195981</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-0.0002654608064157582</v>
       </c>
       <c r="BE3" t="n">
         <v>-0.002193693830830288</v>
@@ -1319,7 +1319,7 @@
         <v>0.01714410928235637</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.006444439882954881</v>
+        <v>0.006441089799202787</v>
       </c>
       <c r="BH3" t="n">
         <v>0.00091226204135468</v>
@@ -1428,7 +1428,7 @@
         <v>0.03874244424109754</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0203958019294971</v>
+        <v>0.02039509367851848</v>
       </c>
       <c r="F4" t="n">
         <v>0.006671256170885193</v>
@@ -1437,28 +1437,28 @@
         <v>0.02552173978531248</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005854098539711553</v>
+        <v>0.005848684401589948</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009357611890632927</v>
+        <v>0.0009346594302296033</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03131641847778766</v>
+        <v>0.03131617875630879</v>
       </c>
       <c r="K4" t="n">
+        <v>0.02039741917741339</v>
+      </c>
+      <c r="L4" t="n">
         <v>0.02040374252961537</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.02040331937409664</v>
       </c>
       <c r="M4" t="n">
         <v>0.02769487937312341</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02292361570272933</v>
+        <v>0.02292103527311747</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05817766552299473</v>
+        <v>0.05817424202139358</v>
       </c>
       <c r="P4" t="n">
         <v>0.01582008530659439</v>
@@ -1467,7 +1467,7 @@
         <v>0.01626062817760141</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01497166854281862</v>
+        <v>0.01496878195216121</v>
       </c>
       <c r="S4" t="n">
         <v>0.1146794662697108</v>
@@ -1479,7 +1479,7 @@
         <v>0.08720404182986519</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0009318808804009417</v>
+        <v>0.0009373257312766618</v>
       </c>
       <c r="W4" t="n">
         <v>0.02899110914767217</v>
@@ -1503,13 +1503,13 @@
         <v>0.05682789149805772</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1328433374190511</v>
+        <v>0.1328428634378307</v>
       </c>
       <c r="AE4" t="n">
         <v>0.1530383818478931</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.103877573857367</v>
+        <v>0.1038772697491748</v>
       </c>
       <c r="AG4" t="n">
         <v>0.06579709336969457</v>
@@ -1569,19 +1569,19 @@
         <v>0.03469325774044062</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.02143409051584357</v>
+        <v>0.02144856546271191</v>
       </c>
       <c r="BA4" t="n">
         <v>0.0202307727851956</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.01489655629858038</v>
+        <v>0.01489650922973701</v>
       </c>
       <c r="BC4" t="n">
+        <v>0.001030497474360625</v>
+      </c>
+      <c r="BD4" t="n">
         <v>0.001028927248853858</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0.001030497474360625</v>
       </c>
       <c r="BE4" t="n">
         <v>0.00368995410870174</v>
@@ -1590,7 +1590,7 @@
         <v>0.05183847200708699</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.03347081537548485</v>
+        <v>0.03347313569399774</v>
       </c>
       <c r="BH4" t="n">
         <v>0.002148954049044732</v>
@@ -1699,7 +1699,7 @@
         <v>-0.06251301631377995</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0067364746945899</v>
+        <v>0.006771378708551512</v>
       </c>
       <c r="F5" t="n">
         <v>-0.004120603015075342</v>
@@ -1840,7 +1840,7 @@
         <v>-0.06564860426929385</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.03106457242582896</v>
+        <v>-0.03113438045375216</v>
       </c>
       <c r="BA5" t="n">
         <v>-0.02118673647469455</v>
@@ -1985,7 +1985,7 @@
         <v>-0.0005431759753611015</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0071147609971038</v>
+        <v>0.007090130455231877</v>
       </c>
       <c r="K6" t="n">
         <v>0.004736526576720934</v>
@@ -2051,7 +2051,7 @@
         <v>0.2072482808212385</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01887622260872879</v>
+        <v>0.01888426895568727</v>
       </c>
       <c r="AG6" t="n">
         <v>0.102820391266503</v>
@@ -2120,10 +2120,10 @@
         <v>-0.001316723658883737</v>
       </c>
       <c r="BC6" t="n">
+        <v>-0.0007470391537774262</v>
+      </c>
+      <c r="BD6" t="n">
         <v>-0.0007383131502870261</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-0.0007470391537774262</v>
       </c>
       <c r="BE6" t="n">
         <v>-0.004761231935899243</v>
@@ -2253,7 +2253,7 @@
         <v>0.001715076832505014</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002013350826381932</v>
+        <v>0.0001849219206312924</v>
       </c>
       <c r="J7" t="n">
         <v>0.02400048807486564</v>
@@ -2262,13 +2262,13 @@
         <v>0.0139697060305125</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01398579872442946</v>
+        <v>0.0139697060305125</v>
       </c>
       <c r="M7" t="n">
         <v>0.01015654568218702</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01236647460317921</v>
+        <v>0.0123838236663298</v>
       </c>
       <c r="O7" t="n">
         <v>0.02815217167078101</v>
@@ -2280,7 +2280,7 @@
         <v>0.01002325232338971</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01713822164925854</v>
+        <v>0.01717242407499982</v>
       </c>
       <c r="S7" t="n">
         <v>0.2540254370026941</v>
@@ -2316,7 +2316,7 @@
         <v>0.03026653469740896</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1513542711081758</v>
+        <v>0.1513381784142588</v>
       </c>
       <c r="AE7" t="n">
         <v>0.2714327768753014</v>
@@ -2388,7 +2388,7 @@
         <v>0.005541292289916127</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0002128093615613891</v>
+        <v>0.0001963890003134405</v>
       </c>
       <c r="BC7" t="n">
         <v>-0.0002556471122987958</v>
@@ -2524,10 +2524,10 @@
         <v>0.003017455648939618</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005194240975671283</v>
+        <v>0.0005192414168256138</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05880622593608063</v>
+        <v>0.05878029232612212</v>
       </c>
       <c r="K8" t="n">
         <v>0.03509094821661944</v>
@@ -2539,10 +2539,10 @@
         <v>0.02058558408831454</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0268526673009614</v>
+        <v>0.02682703503848704</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04425302499830426</v>
+        <v>0.04426156908579571</v>
       </c>
       <c r="P8" t="n">
         <v>0.02645177300086677</v>
@@ -2551,7 +2551,7 @@
         <v>0.01391684540504872</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02261994232004565</v>
+        <v>0.02264587593000416</v>
       </c>
       <c r="S8" t="n">
         <v>0.3929603578198232</v>
@@ -2801,7 +2801,7 @@
         <v>0.08278375564040263</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05141361256544508</v>
+        <v>0.05137870855148348</v>
       </c>
       <c r="L9" t="n">
         <v>0.05141361256544508</v>
@@ -2822,7 +2822,7 @@
         <v>0.04297036526533429</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03735475051264522</v>
+        <v>0.03734814300590069</v>
       </c>
       <c r="S9" t="n">
         <v>0.451440472058313</v>
